--- a/01_用AI生成Excel/07_條件式格式/專案進度管控表.xlsx
+++ b/01_用AI生成Excel/07_條件式格式/專案進度管控表.xlsx
@@ -208,8 +208,12 @@
     <tableColumn id="6" name="完成進度"/>
     <tableColumn id="7" name="預算"/>
     <tableColumn id="8" name="實際支出"/>
-    <tableColumn id="9" name="剩餘預算"/>
-    <tableColumn id="10" name="預算使用率"/>
+    <tableColumn id="9" name="剩餘預算">
+      <calculatedColumnFormula>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" name="預算使用率">
+      <calculatedColumnFormula>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -605,11 +609,11 @@
         <v>28000</v>
       </c>
       <c r="I2" s="5">
-        <f>G2-H2</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J2" s="4">
-        <f>IF(G2=0,0,H2/G2)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -647,11 +651,11 @@
         <v>86000</v>
       </c>
       <c r="I3" s="5">
-        <f>G3-H3</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>IF(G3=0,0,H3/G3)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -689,11 +693,11 @@
         <v>45000</v>
       </c>
       <c r="I4" s="5">
-        <f>G4-H4</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J4" s="4">
-        <f>IF(G4=0,0,H4/G4)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -731,11 +735,11 @@
         <v>120000</v>
       </c>
       <c r="I5" s="5">
-        <f>G5-H5</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J5" s="4">
-        <f>IF(G5=0,0,H5/G5)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -773,11 +777,11 @@
         <v>192000</v>
       </c>
       <c r="I6" s="5">
-        <f>G6-H6</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J6" s="4">
-        <f>IF(G6=0,0,H6/G6)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -815,11 +819,11 @@
         <v>52000</v>
       </c>
       <c r="I7" s="5">
-        <f>G7-H7</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J7" s="4">
-        <f>IF(G7=0,0,H7/G7)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -857,11 +861,11 @@
         <v>8000</v>
       </c>
       <c r="I8" s="5">
-        <f>G8-H8</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J8" s="4">
-        <f>IF(G8=0,0,H8/G8)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -899,11 +903,11 @@
         <v>0</v>
       </c>
       <c r="I9" s="5">
-        <f>G9-H9</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J9" s="4">
-        <f>IF(G9=0,0,H9/G9)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -941,11 +945,11 @@
         <v>12000</v>
       </c>
       <c r="I10" s="5">
-        <f>G10-H10</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J10" s="4">
-        <f>IF(G10=0,0,H10/G10)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -983,11 +987,11 @@
         <v>0</v>
       </c>
       <c r="I11" s="5">
-        <f>G11-H11</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J11" s="4">
-        <f>IF(G11=0,0,H11/G11)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -1025,11 +1029,11 @@
         <v>47500</v>
       </c>
       <c r="I12" s="5">
-        <f>G12-H12</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J12" s="4">
-        <f>IF(G12=0,0,H12/G12)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
@@ -1067,31 +1071,31 @@
         <v>0</v>
       </c>
       <c r="I13" s="5">
-        <f>G13-H13</f>
+        <f>T_Project[[#This Row],[預算]]-T_Project[[#This Row],[實際支出]]</f>
         <v/>
       </c>
       <c r="J13" s="4">
-        <f>IF(G13=0,0,H13/G13)</f>
+        <f>IF(T_Project[[#This Row],[預算]]=0,0,T_Project[[#This Row],[實際支出]]/T_Project[[#This Row],[預算]])</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I13">
+  <conditionalFormatting sqref="I2:I200">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:J13">
+  <conditionalFormatting sqref="A2:J200">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>AND($D2&lt;基準日,$E2&lt;&gt;"已完成")</formula>
+      <formula>AND($D2&lt;&gt;"",$D2&lt;基準日,$E2&lt;&gt;"已完成")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E200">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>$E2="已完成"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F2:F200">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
